--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erico\Desktop\projects\greenland_lowthreshold_system\FLOWER-board-firmware\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\clean\FLOWER-BOARD-Firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B20BF66-5D7C-4842-8203-FA81531C5763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="600" windowWidth="23235" windowHeight="14700"/>
+    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Registers" sheetId="1" r:id="rId1"/>
+    <sheet name="Scalers" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="261">
   <si>
     <t>Register Map</t>
   </si>
@@ -131,24 +135,15 @@
     <t>channel mask</t>
   </si>
   <si>
-    <t>trigger mask</t>
-  </si>
-  <si>
     <t>set beam bit to 0 to mask</t>
   </si>
   <si>
-    <t>beam mask in trigger [LSB-&gt;(num_beams-1)]</t>
-  </si>
-  <si>
     <t>rdout-&gt;pretrigger window</t>
   </si>
   <si>
     <t>read_only - board DNA (FPGA silicon-specific ID)</t>
   </si>
   <si>
-    <t>current 32 bit register space: 8 bit address + 24 bit data (i.e. 128 24-bit registers)</t>
-  </si>
-  <si>
     <t>rdout-&gt;wfm buffer</t>
   </si>
   <si>
@@ -188,9 +183,6 @@
     <t>bit0-&gt;global reset, bit1-&gt;reset global EXCEPT register settings, bit2-&gt;reset ADC (restart+cal cycle)</t>
   </si>
   <si>
-    <t>trigger holdoff</t>
-  </si>
-  <si>
     <t>xFFFFFF</t>
   </si>
   <si>
@@ -314,12 +306,6 @@
     <t>write LSB to update, set LSB+1 to '1' to enable</t>
   </si>
   <si>
-    <t xml:space="preserve">set trigger holdoff </t>
-  </si>
-  <si>
-    <t>lower 16 bits -&gt; max trig hold off is 2^16 * 1/(93.75 MHz) = 709 microsecs</t>
-  </si>
-  <si>
     <t>trigger verification mode</t>
   </si>
   <si>
@@ -410,9 +396,6 @@
     <t>x000700</t>
   </si>
   <si>
-    <t>x0001FF</t>
-  </si>
-  <si>
     <t>if LSB=0, ext trig input acts as 'gate only' for scalers</t>
   </si>
   <si>
@@ -515,9 +498,6 @@
     <t>lowest byte : nominal trigger thresh ; middle byte : servo trigger threshold</t>
   </si>
   <si>
-    <t>COINC TRIGGER-&gt; mask and num_coinc</t>
-  </si>
-  <si>
     <t>toggle FPGA-generated fast pulse w/ LSB, toggle RF switch with LSB+1, bit8 is freq select (0=fastest, 1=8x slower)</t>
   </si>
   <si>
@@ -566,9 +546,6 @@
     <t>read_only - event meta data [lowest 4 bits=trigger type, bit16=pps flag]</t>
   </si>
   <si>
-    <t>currently 32 scalers registers (12 bits per scaler, 2 scalers per 24 bit register)</t>
-  </si>
-  <si>
     <t>data in max_address location may not be useful</t>
   </si>
   <si>
@@ -603,12 +580,252 @@
   </si>
   <si>
     <t>low-byte LSB sends  coinc trig to SMA output; middle byte LSB sends delayed pps to SMA output</t>
+  </si>
+  <si>
+    <t>event metadata-&gt; coinc trig bits</t>
+  </si>
+  <si>
+    <t>event metadata-&gt; phased trig bits</t>
+  </si>
+  <si>
+    <t>event metadata-&gt; beam 0 power</t>
+  </si>
+  <si>
+    <t>event metadata-&gt; pps counter</t>
+  </si>
+  <si>
+    <t>read only - event meta data</t>
+  </si>
+  <si>
+    <t>read only - lowest 4 bits are channels triggering in simple trigger</t>
+  </si>
+  <si>
+    <t>COINC TRIG CHANNEL MASK</t>
+  </si>
+  <si>
+    <t>lowest 4 bits are masks</t>
+  </si>
+  <si>
+    <t>current 32 bit register space: 8 bit address + 24 bit data (i.e. 256 24-bit registers)</t>
+  </si>
+  <si>
+    <t>1Hz</t>
+  </si>
+  <si>
+    <t>Ch 0 Trigger</t>
+  </si>
+  <si>
+    <t>Ch 1 Trigger</t>
+  </si>
+  <si>
+    <t>Ch 2 Trigger</t>
+  </si>
+  <si>
+    <t>Ch 3 Trigger</t>
+  </si>
+  <si>
+    <t>Coinc Trigger</t>
+  </si>
+  <si>
+    <t>Coinc Servo</t>
+  </si>
+  <si>
+    <t>Ch 0 Servo</t>
+  </si>
+  <si>
+    <t>Ch 1 Servo</t>
+  </si>
+  <si>
+    <t>Ch 2 Servo</t>
+  </si>
+  <si>
+    <t>Ch 3 Servo</t>
+  </si>
+  <si>
+    <t>Scaler Num</t>
+  </si>
+  <si>
+    <t>Scaler</t>
+  </si>
+  <si>
+    <t>1Hz Gated</t>
+  </si>
+  <si>
+    <t>100Hz</t>
+  </si>
+  <si>
+    <t>empty</t>
+  </si>
+  <si>
+    <t>Beam 0 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 1 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 2 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 3 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 4 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 5 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 6 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 7 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 8 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 9 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 10 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 11 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 12 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 13 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 14 Trigger</t>
+  </si>
+  <si>
+    <t>Beam 15 Trigger</t>
+  </si>
+  <si>
+    <t>Phased Trigger</t>
+  </si>
+  <si>
+    <t>Beam 0 Servo</t>
+  </si>
+  <si>
+    <t>Beam 1 Servo</t>
+  </si>
+  <si>
+    <t>Beam 2 Servo</t>
+  </si>
+  <si>
+    <t>Beam 3 Servo</t>
+  </si>
+  <si>
+    <t>Phased Servo</t>
+  </si>
+  <si>
+    <t>Beam 15 Servo</t>
+  </si>
+  <si>
+    <t>Beam 14 Servo</t>
+  </si>
+  <si>
+    <t>Beam 13 Servo</t>
+  </si>
+  <si>
+    <t>Beam 12 Servo</t>
+  </si>
+  <si>
+    <t>Beam 11 Servo</t>
+  </si>
+  <si>
+    <t>Beam 10 Servo</t>
+  </si>
+  <si>
+    <t>Beam 9 Servo</t>
+  </si>
+  <si>
+    <t>Beam 8 Servo</t>
+  </si>
+  <si>
+    <t>Beam 7 Servo</t>
+  </si>
+  <si>
+    <t>Beam 6 Servo</t>
+  </si>
+  <si>
+    <t>Beam 5 Servo</t>
+  </si>
+  <si>
+    <t>Beam 4 Servo</t>
+  </si>
+  <si>
+    <t>COINC TRIGGER-&gt;num_coinc, window, and vpp mode</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 0 thresholds</t>
+  </si>
+  <si>
+    <t>Lower 12 bits are the trig thresholds, upper 12 are servo thresholds</t>
+  </si>
+  <si>
+    <t>0xFFFFFF</t>
+  </si>
+  <si>
+    <t>Scaler Address</t>
+  </si>
+  <si>
+    <t>Update Rate</t>
+  </si>
+  <si>
+    <t>read only - debug only at the moment</t>
+  </si>
+  <si>
+    <t>read only - lowest 16 bits are beams triggering in phased trigger</t>
+  </si>
+  <si>
+    <t>currently 133 scalers registers (12 bits per scaler, 2 scalers per 24 bit register)</t>
+  </si>
+  <si>
+    <t>Scaler PPS</t>
+  </si>
+  <si>
+    <t>PPS counter lowest 12 bits</t>
+  </si>
+  <si>
+    <t>PPS counter 12-23 bits</t>
+  </si>
+  <si>
+    <t>PPS counter 24-35 bits</t>
+  </si>
+  <si>
+    <t>PPS counter highest 12 bits</t>
+  </si>
+  <si>
+    <t>* This matches the scaler array type in scalers_top.vhd!</t>
+  </si>
+  <si>
+    <t>trigger mask + power threhold low bit</t>
+  </si>
+  <si>
+    <t>HB is place of low bit of the threshold power, beam mask in trigger [MB+LB-&gt;(num_beams-1)]</t>
+  </si>
+  <si>
+    <t>thresholds offset</t>
+  </si>
+  <si>
+    <t>sets the offset to the servo and trigger phased thresholds (0 offset can saturate trigger rates &gt;1Hz)</t>
+  </si>
+  <si>
+    <t>x000BB8</t>
+  </si>
+  <si>
+    <t>lower 12 bits are threshold offset (ie. Bumps all SBC thresholds up by x amount)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -698,12 +915,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -798,12 +1021,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -813,29 +1034,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -845,15 +1058,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -861,7 +1068,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -884,13 +1090,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -902,14 +1105,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1189,72 +1397,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G134"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G262"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" customWidth="1"/>
-    <col min="4" max="4" width="87.28515625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="74.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="60.33203125" customWidth="1"/>
+    <col min="4" max="4" width="87.33203125" customWidth="1"/>
+    <col min="5" max="5" width="23.44140625" customWidth="1"/>
+    <col min="6" max="6" width="74.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="59">
-        <v>44212</v>
-      </c>
-      <c r="B4" s="60"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="45">
+        <v>45372</v>
+      </c>
+      <c r="B4" s="44"/>
       <c r="C4" s="1"/>
       <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>2</v>
@@ -1265,30 +1473,30 @@
       <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0</v>
       </c>
-      <c r="B7" s="24" t="str">
+      <c r="B7" s="16" t="str">
         <f>"x" &amp; DEC2HEX(A7,2)</f>
         <v>x00</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="24" t="str">
+      <c r="B8" s="16" t="str">
         <f t="shared" ref="B8:B71" si="0">"x" &amp; DEC2HEX(A8,2)</f>
         <v>x01</v>
       </c>
@@ -1299,12 +1507,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>1+A8</f>
         <v>2</v>
       </c>
-      <c r="B9" s="24" t="str">
+      <c r="B9" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x02</v>
       </c>
@@ -1315,31 +1523,31 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" ref="A10:A73" si="1">1+A9</f>
         <v>3</v>
       </c>
-      <c r="B10" s="24" t="str">
+      <c r="B10" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x03</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B11" s="24" t="str">
+      <c r="B11" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x04</v>
       </c>
@@ -1347,954 +1555,931 @@
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B12" s="24" t="str">
+      <c r="B12" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x05</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B13" s="24" t="str">
+      <c r="B13" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x06</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B14" s="24" t="str">
+      <c r="B14" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x07</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B15" s="24" t="str">
+      <c r="B15" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x08</v>
       </c>
-      <c r="C15" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="50" t="s">
+      <c r="C15" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="34" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B16" s="24" t="str">
+      <c r="B16" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x09</v>
       </c>
-      <c r="C16" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="50" t="s">
+      <c r="C16" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="34" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B17" s="25" t="str">
+      <c r="B17" s="17" t="str">
         <f t="shared" si="0"/>
         <v>x0A</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="C17" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+      <c r="F17" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B18" s="26" t="str">
+      <c r="B18" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x0B</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="18" t="s">
+      <c r="C18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B19" s="26" t="str">
+      <c r="B19" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x0C</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="18" t="s">
+      <c r="C19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E19" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B20" s="26" t="str">
+      <c r="B20" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x0D</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="18" t="s">
+      <c r="C20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B21" s="26" t="str">
+      <c r="B21" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x0E</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="C21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="19"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B22" s="26" t="str">
+      <c r="B22" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x0F</v>
       </c>
-      <c r="F22" s="19"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+      <c r="C22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B23" s="26" t="str">
+      <c r="B23" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x10</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="19"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+      <c r="C23" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B24" s="26" t="str">
+      <c r="B24" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x11</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
+      <c r="C24" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="13"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B25" s="26" t="str">
+      <c r="B25" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x12</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="19"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+      <c r="C25" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B26" s="26" t="str">
+      <c r="B26" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x13</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="19"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B27" s="26" t="str">
+      <c r="B27" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x14</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="19"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+      <c r="F27" s="13"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B28" s="26" t="str">
+      <c r="B28" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x15</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="19"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B29" s="26" t="str">
+      <c r="B29" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x16</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="19"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="17">
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B30" s="26" t="str">
+      <c r="B30" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x17</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="19"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="17">
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B31" s="26" t="str">
+      <c r="B31" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x18</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="19"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="17">
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B32" s="26" t="str">
+      <c r="B32" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x19</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="19"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="17">
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B33" s="26" t="str">
+      <c r="B33" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x1A</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="19"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="17">
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B34" s="26" t="str">
+      <c r="B34" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x1B</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="19"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="17">
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B35" s="26" t="str">
+      <c r="B35" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x1C</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="19"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="17">
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B36" s="26" t="str">
+      <c r="B36" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x1D</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="19"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="17">
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="12">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="B37" s="26" t="str">
+      <c r="B37" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x1E</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="19"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="17">
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B38" s="26" t="str">
+      <c r="B38" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x1F</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="17">
+      <c r="F38" s="13"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="12">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="B39" s="26" t="str">
+      <c r="B39" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x20</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="19"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="17">
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="B40" s="26" t="str">
+      <c r="B40" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x21</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="19"/>
-    </row>
-    <row r="41" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="41">
+      <c r="F40" s="13"/>
+    </row>
+    <row r="41" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="28">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="B41" s="42" t="str">
+      <c r="B41" s="29" t="str">
         <f t="shared" si="0"/>
         <v>x22</v>
       </c>
-      <c r="C41" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C41" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="31"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B42" s="24" t="str">
+      <c r="B42" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x23</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D42" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B43" s="24" t="str">
+      <c r="B43" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x24</v>
       </c>
-      <c r="C43" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B44" s="24" t="str">
+      <c r="B44" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x25</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" t="s">
         <v>60</v>
       </c>
-      <c r="D44" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B45" s="24" t="str">
+      <c r="B45" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x26</v>
       </c>
-      <c r="C45" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="53">
+      <c r="C45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="37">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B46" s="54" t="str">
+      <c r="B46" s="38" t="str">
         <f t="shared" si="0"/>
         <v>x27</v>
       </c>
-      <c r="C46" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="53" t="s">
+      <c r="C46" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="F46" s="56" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F46" s="39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="B47" s="24" t="str">
+      <c r="B47" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x28</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="B48" s="24" t="str">
+      <c r="B48" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x29</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F48" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="B49" s="24" t="str">
+      <c r="B49" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x2A</v>
       </c>
       <c r="C49" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>161</v>
+      <c r="D49" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="E49" t="s">
         <v>6</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B50" s="24" t="str">
+      <c r="B50" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x2B</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B51" s="24" t="str">
+      <c r="B51" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x2C</v>
       </c>
       <c r="C51" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="B52" s="24" t="str">
+      <c r="B52" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x2D</v>
       </c>
-      <c r="C52" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" t="s">
+        <v>127</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B53" s="24" t="str">
+      <c r="B53" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x2E</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B54" s="24" t="str">
+      <c r="B54" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x2F</v>
       </c>
-      <c r="D54" s="5"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D54" s="3"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="B55" s="24" t="str">
+      <c r="B55" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x30</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D55" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="E55" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D55" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="B56" s="24" t="str">
+      <c r="B56" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x31</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="B57" s="24" t="str">
+      <c r="B57" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x32</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="B58" s="24" t="str">
+      <c r="B58" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x33</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="B59" s="24" t="str">
+      <c r="B59" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x34</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B60" s="24" t="str">
+      <c r="B60" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x35</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B61" s="24" t="str">
+      <c r="B61" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x36</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="B62" s="24" t="str">
+      <c r="B62" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x37</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="B63" s="24" t="str">
+      <c r="B63" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x38</v>
       </c>
       <c r="C63" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" t="s">
         <v>6</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F63" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B64" s="24" t="str">
+      <c r="B64" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x39</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" t="s">
         <v>22</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E64" s="3" t="s">
+      <c r="D64" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" t="s">
         <v>6</v>
       </c>
-      <c r="F64" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F64" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="B65" s="24" t="str">
+      <c r="B65" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x3A</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E65" s="34" t="s">
+      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E65" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="B66" s="24" t="str">
+      <c r="B66" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x3B</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E66" s="34" t="s">
+      <c r="C66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E66" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="B67" s="24" t="str">
+      <c r="B67" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x3C</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E67" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E67" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="B68" s="24" t="str">
+      <c r="B68" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x3D</v>
       </c>
-      <c r="C68" t="s">
-        <v>164</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E68" s="46" t="s">
+      <c r="C68" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="B69" s="24" t="str">
+      <c r="B69" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x3E</v>
       </c>
-      <c r="C69" s="30"/>
-      <c r="D69" s="5"/>
-      <c r="F69" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="B70" s="24" t="str">
+      <c r="B70" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x3F</v>
       </c>
-      <c r="C70" s="30"/>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D70" s="3"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="B71" s="24" t="str">
+      <c r="B71" s="16" t="str">
         <f t="shared" si="0"/>
         <v>x40</v>
       </c>
@@ -2308,798 +2493,782 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="B72" s="24" t="str">
-        <f t="shared" ref="B72:B134" si="2">"x" &amp; DEC2HEX(A72,2)</f>
+      <c r="B72" s="16" t="str">
+        <f t="shared" ref="B72:B136" si="2">"x" &amp; DEC2HEX(A72,2)</f>
         <v>x41</v>
       </c>
       <c r="C72" t="s">
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E72" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="B73" s="24" t="str">
+      <c r="B73" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x42</v>
       </c>
       <c r="C73" t="s">
-        <v>151</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8">
+        <v>144</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74">
         <f t="shared" ref="A74:A134" si="3">1+A73</f>
         <v>67</v>
       </c>
-      <c r="B74" s="24" t="str">
+      <c r="B74" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x43</v>
       </c>
-      <c r="F74" s="10"/>
-    </row>
-    <row r="75" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="8">
+      <c r="F74" s="7"/>
+    </row>
+    <row r="75" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75">
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-      <c r="B75" s="24" t="str">
+      <c r="B75" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x44</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F75" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="D75" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="F75" s="29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="8">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
         <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="B76" s="24" t="str">
+      <c r="B76" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x45</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" t="s">
         <v>24</v>
       </c>
-      <c r="D76" s="8" t="s">
-        <v>65</v>
+      <c r="D76" t="s">
+        <v>61</v>
       </c>
       <c r="E76" t="s">
         <v>7</v>
       </c>
-      <c r="F76" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
+      <c r="F76" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="B77" s="24" t="str">
+      <c r="B77" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x46</v>
       </c>
-      <c r="F77" s="10"/>
-    </row>
-    <row r="78" spans="1:6" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
+      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:6" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78">
         <f t="shared" si="3"/>
         <v>71</v>
       </c>
-      <c r="B78" s="24" t="str">
+      <c r="B78" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x47</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F78" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
+      <c r="F78" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="B79" s="24" t="str">
+      <c r="B79" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x48</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" t="s">
         <v>12</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" t="s">
         <v>7</v>
       </c>
-      <c r="F79" s="22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
+      <c r="F79" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80">
         <f t="shared" si="3"/>
         <v>73</v>
       </c>
-      <c r="B80" s="24" t="str">
+      <c r="B80" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x49</v>
       </c>
-      <c r="E80" s="4"/>
-    </row>
-    <row r="81" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="8">
+    </row>
+    <row r="81" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81">
         <f t="shared" si="3"/>
         <v>74</v>
       </c>
-      <c r="B81" s="24" t="str">
+      <c r="B81" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x4A</v>
       </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="12"/>
-      <c r="F81" s="10"/>
-    </row>
-    <row r="82" spans="1:6" s="9" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
+      <c r="C81"/>
+      <c r="D81" s="8"/>
+      <c r="F81" s="7"/>
+    </row>
+    <row r="82" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82">
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
-      <c r="B82" s="24" t="str">
+      <c r="B82" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x4B</v>
       </c>
-      <c r="C82" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="D82" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="E82" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="F82" s="52" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C82" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E82" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" s="36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="3"/>
         <v>76</v>
       </c>
-      <c r="B83" s="24" t="str">
+      <c r="B83" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x4C</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>184</v>
+        <v>33</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="E83" t="s">
-        <v>179</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" si="3"/>
         <v>77</v>
       </c>
-      <c r="B84" s="24" t="str">
+      <c r="B84" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x4D</v>
       </c>
       <c r="C84" t="s">
-        <v>78</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>166</v>
+        <v>74</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="E84" t="s">
         <v>7</v>
       </c>
-      <c r="F84" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F84" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="3"/>
         <v>78</v>
       </c>
-      <c r="B85" s="24" t="str">
+      <c r="B85" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x4E</v>
       </c>
-      <c r="C85" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="D85" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85" s="50" t="s">
+      <c r="C85" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="F85" s="51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F85" s="35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="3"/>
         <v>79</v>
       </c>
-      <c r="B86" s="24" t="str">
+      <c r="B86" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x4F</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
-      <c r="B87" s="24" t="str">
+      <c r="B87" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x50</v>
       </c>
-      <c r="C87" s="47" t="s">
+      <c r="C87" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D87" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="E87" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D87" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="E87" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="F87" s="48" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="3"/>
         <v>81</v>
       </c>
-      <c r="B88" s="24" t="str">
+      <c r="B88" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x51</v>
       </c>
-      <c r="C88" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="D88" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="E88" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="F88" s="48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C88" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="D88" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="E88" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F88" s="43" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="3"/>
         <v>82</v>
       </c>
-      <c r="B89" s="24" t="str">
+      <c r="B89" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x52</v>
       </c>
-      <c r="C89" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="D89" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="E89" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="F89" s="48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="C89" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D89" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="E89" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" s="33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="3"/>
         <v>83</v>
       </c>
-      <c r="B90" s="24" t="str">
+      <c r="B90" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x53</v>
       </c>
-      <c r="C90" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="D90" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="F90" s="48" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="C90" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="E90" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="F90" s="33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="3"/>
         <v>84</v>
       </c>
-      <c r="B91" s="24" t="str">
+      <c r="B91" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x54</v>
       </c>
-      <c r="C91" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="E91" s="47" t="s">
+      <c r="C91" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E91" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="F91" s="48" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F91" s="33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="3"/>
         <v>85</v>
       </c>
-      <c r="B92" s="24" t="str">
+      <c r="B92" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x55</v>
       </c>
-      <c r="C92" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="D92" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" s="47" t="s">
+      <c r="C92" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E92" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="48"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F92" s="33"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93">
         <f t="shared" si="3"/>
         <v>86</v>
       </c>
-      <c r="B93" s="24" t="str">
+      <c r="B93" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x56</v>
       </c>
-      <c r="E93" s="11"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94">
         <f t="shared" si="3"/>
         <v>87</v>
       </c>
-      <c r="B94" s="24" t="str">
+      <c r="B94" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x57</v>
       </c>
-      <c r="C94" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E94" s="45" t="s">
+      <c r="C94" t="s">
+        <v>148</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E94" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <f t="shared" si="3"/>
         <v>88</v>
       </c>
-      <c r="B95" s="24" t="str">
+      <c r="B95" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x58</v>
       </c>
-      <c r="C95" s="45" t="s">
-        <v>156</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E95" s="45" t="s">
+      <c r="C95" t="s">
+        <v>149</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E95" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <f t="shared" si="3"/>
         <v>89</v>
       </c>
-      <c r="B96" s="24" t="str">
+      <c r="B96" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x59</v>
       </c>
-      <c r="C96" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E96" s="45" t="s">
+      <c r="C96" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E96" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97">
         <f t="shared" si="3"/>
         <v>90</v>
       </c>
-      <c r="B97" s="24" t="str">
+      <c r="B97" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x5A</v>
       </c>
-      <c r="C97" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E97" s="45" t="s">
+      <c r="C97" t="s">
+        <v>151</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E97" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98">
         <f t="shared" si="3"/>
         <v>91</v>
       </c>
-      <c r="B98" s="24" t="str">
+      <c r="B98" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x5B</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E98" s="45" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>240</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E98" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99">
         <f t="shared" si="3"/>
         <v>92</v>
       </c>
-      <c r="B99" s="24" t="str">
+      <c r="B99" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x5C</v>
       </c>
-      <c r="C99" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E99" s="49" t="s">
+      <c r="C99" t="s">
+        <v>173</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E99" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100">
         <f t="shared" si="3"/>
         <v>93</v>
       </c>
-      <c r="B100" s="24" t="str">
+      <c r="B100" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x5D</v>
       </c>
-      <c r="C100" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E100" s="49" t="s">
+      <c r="C100" t="s">
+        <v>174</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E100" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101">
         <f t="shared" si="3"/>
         <v>94</v>
       </c>
-      <c r="B101" s="24" t="str">
+      <c r="B101" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x5E</v>
       </c>
-      <c r="C101" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E101" s="57" t="s">
+      <c r="C101" t="s">
+        <v>177</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E101" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102">
         <f t="shared" si="3"/>
         <v>95</v>
       </c>
-      <c r="B102" s="24" t="str">
+      <c r="B102" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x5F</v>
       </c>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C102" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D102" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="E102" s="40"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="B103" s="24" t="str">
+      <c r="B103" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x60</v>
       </c>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104">
         <f t="shared" si="3"/>
         <v>97</v>
       </c>
-      <c r="B104" s="24" t="str">
+      <c r="B104" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x61</v>
       </c>
-      <c r="C104" s="11"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105">
         <f t="shared" si="3"/>
         <v>98</v>
       </c>
-      <c r="B105" s="24" t="str">
+      <c r="B105" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x62</v>
       </c>
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106">
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="B106" s="24" t="str">
+      <c r="B106" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x63</v>
       </c>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="B107" s="24" t="str">
+      <c r="B107" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x64</v>
       </c>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108">
         <f t="shared" si="3"/>
         <v>101</v>
       </c>
-      <c r="B108" s="24" t="str">
+      <c r="B108" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x65</v>
       </c>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-    </row>
-    <row r="109" spans="1:6" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="35">
+    </row>
+    <row r="109" spans="1:6" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="22">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="B109" s="36" t="str">
+      <c r="B109" s="23" t="str">
         <f t="shared" si="2"/>
         <v>x66</v>
       </c>
-      <c r="D109" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="E109" s="35" t="s">
+      <c r="D109" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E109" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F109" s="37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="31">
+      <c r="F109" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="19">
         <f t="shared" si="3"/>
         <v>103</v>
       </c>
-      <c r="B110" s="32" t="str">
+      <c r="B110" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x67</v>
       </c>
-      <c r="C110" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D110" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="F110" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="31">
+      <c r="C110" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="19">
         <f t="shared" si="3"/>
         <v>104</v>
       </c>
-      <c r="B111" s="32" t="str">
+      <c r="B111" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x68</v>
       </c>
-      <c r="C111" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="F111" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="31">
+      <c r="C111" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F111" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="19">
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="B112" s="32" t="str">
+      <c r="B112" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x69</v>
       </c>
-      <c r="C112" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="F112" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="31">
+      <c r="C112" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F112" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="19">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
-      <c r="B113" s="32" t="str">
+      <c r="B113" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x6A</v>
       </c>
-      <c r="C113" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="F113" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="31">
+      <c r="C113" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F113" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="19">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="B114" s="32" t="str">
+      <c r="B114" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x6B</v>
       </c>
-      <c r="C114" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F114" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C114" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <f t="shared" si="3"/>
         <v>108</v>
       </c>
-      <c r="B115" s="24" t="str">
+      <c r="B115" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x6C</v>
       </c>
-      <c r="C115" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D115" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E115" s="27" t="s">
+      <c r="C115" t="s">
+        <v>86</v>
+      </c>
+      <c r="D115" t="s">
+        <v>88</v>
+      </c>
+      <c r="E115" t="s">
         <v>6</v>
       </c>
-      <c r="F115" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F115" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <f t="shared" si="3"/>
         <v>109</v>
       </c>
-      <c r="B116" s="24" t="str">
+      <c r="B116" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x6D</v>
       </c>
       <c r="C116" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
@@ -3107,328 +3276,1752 @@
       <c r="E116" t="s">
         <v>19</v>
       </c>
-      <c r="F116" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="31">
+      <c r="F116" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="19">
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
-      <c r="B117" s="32" t="str">
+      <c r="B117" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x6E</v>
       </c>
-      <c r="C117" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D117" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="F117" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="31">
+      <c r="C117" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F117" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="19">
         <f t="shared" si="3"/>
         <v>111</v>
       </c>
-      <c r="B118" s="32" t="str">
+      <c r="B118" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x6F</v>
       </c>
-      <c r="C118" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D118" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="F118" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="31">
+      <c r="C118" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F118" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="19">
         <f t="shared" si="3"/>
         <v>112</v>
       </c>
-      <c r="B119" s="32" t="str">
+      <c r="B119" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x70</v>
       </c>
-      <c r="C119" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D119" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F119" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="31">
+      <c r="C119" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F119" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="19">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="B120" s="32" t="str">
+      <c r="B120" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x71</v>
       </c>
-      <c r="C120" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D120" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F120" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="31">
+      <c r="C120" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F120" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="19">
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
-      <c r="B121" s="32" t="str">
+      <c r="B121" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x72</v>
       </c>
-      <c r="C121" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D121" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="F121" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="31">
+      <c r="C121" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F121" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="19">
         <f t="shared" si="3"/>
         <v>115</v>
       </c>
-      <c r="B122" s="32" t="str">
+      <c r="B122" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x73</v>
       </c>
-      <c r="C122" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D122" s="31" t="s">
+      <c r="C122" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="F122" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="31">
+      <c r="D122" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="19">
         <f t="shared" si="3"/>
         <v>116</v>
       </c>
-      <c r="B123" s="32" t="str">
+      <c r="B123" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x74</v>
       </c>
-      <c r="C123" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="D123" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F123" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="31">
+      <c r="C123" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F123" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="19">
         <f t="shared" si="3"/>
         <v>117</v>
       </c>
-      <c r="B124" s="32" t="str">
+      <c r="B124" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x75</v>
       </c>
-      <c r="C124" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="D124" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="F124" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="31">
+      <c r="C124" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F124" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="19">
         <f t="shared" si="3"/>
         <v>118</v>
       </c>
-      <c r="B125" s="32" t="str">
+      <c r="B125" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x76</v>
       </c>
-      <c r="C125" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="D125" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F125" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="31">
+      <c r="C125" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F125" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="19">
         <f t="shared" si="3"/>
         <v>119</v>
       </c>
-      <c r="B126" s="32" t="str">
+      <c r="B126" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x77</v>
       </c>
-      <c r="C126" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D126" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="F126" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="31">
+      <c r="C126" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F126" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="19">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="B127" s="32" t="str">
+      <c r="B127" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x78</v>
       </c>
-      <c r="C127" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="F127" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="31">
+      <c r="C127" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F127" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="19">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="B128" s="32" t="str">
+      <c r="B128" s="20" t="str">
         <f t="shared" si="2"/>
         <v>x79</v>
       </c>
-      <c r="C128" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D128" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="F128" s="33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C128" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F128" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129">
         <f t="shared" si="3"/>
         <v>122</v>
       </c>
-      <c r="B129" s="24" t="str">
+      <c r="B129" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x7A</v>
       </c>
     </row>
-    <row r="130" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="38">
+    <row r="130" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="25">
         <f t="shared" si="3"/>
         <v>123</v>
       </c>
-      <c r="B130" s="39" t="str">
+      <c r="B130" s="26" t="str">
         <f t="shared" si="2"/>
         <v>x7B</v>
       </c>
-      <c r="C130" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="F130" s="40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="38">
+      <c r="C130" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F130" s="27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="25">
         <f t="shared" si="3"/>
         <v>124</v>
       </c>
-      <c r="B131" s="39" t="str">
+      <c r="B131" s="26" t="str">
         <f t="shared" si="2"/>
         <v>x7C</v>
       </c>
-      <c r="C131" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="F131" s="40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C131" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F131" s="27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132">
         <f t="shared" si="3"/>
         <v>125</v>
       </c>
-      <c r="B132" s="24" t="str">
+      <c r="B132" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x7D</v>
       </c>
-      <c r="C132" s="31"/>
-      <c r="D132" s="31"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C132" s="19"/>
+      <c r="D132" s="19"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133">
         <f t="shared" si="3"/>
         <v>126</v>
       </c>
-      <c r="B133" s="24" t="str">
+      <c r="B133" s="16" t="str">
         <f t="shared" si="2"/>
         <v>x7E</v>
       </c>
       <c r="C133" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D133" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E133" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="53">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="37">
         <f t="shared" si="3"/>
         <v>127</v>
       </c>
-      <c r="B134" s="54" t="str">
+      <c r="B134" s="38" t="str">
         <f t="shared" si="2"/>
         <v>x7F</v>
       </c>
-      <c r="C134" s="53" t="s">
+      <c r="C134" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D134" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E134" s="53" t="s">
+      <c r="D134" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E134" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="F134" s="5" t="s">
+      <c r="F134" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <f>A134+1</f>
+        <v>128</v>
+      </c>
+      <c r="B135" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>x80</v>
+      </c>
+      <c r="C135" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D135" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E135" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <f t="shared" ref="A136:A199" si="4">A135+1</f>
+        <v>129</v>
+      </c>
+      <c r="B136" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>x81</v>
+      </c>
+      <c r="C136" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D136" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E136" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <f t="shared" si="4"/>
+        <v>130</v>
+      </c>
+      <c r="B137" s="16" t="str">
+        <f t="shared" ref="B137:B200" si="5">"x" &amp; DEC2HEX(A137,2)</f>
+        <v>x82</v>
+      </c>
+      <c r="C137" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D137" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E137" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <f t="shared" si="4"/>
+        <v>131</v>
+      </c>
+      <c r="B138" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x83</v>
+      </c>
+      <c r="C138" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D138" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E138" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <f t="shared" si="4"/>
+        <v>132</v>
+      </c>
+      <c r="B139" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x84</v>
+      </c>
+      <c r="C139" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D139" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E139" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <f t="shared" si="4"/>
+        <v>133</v>
+      </c>
+      <c r="B140" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x85</v>
+      </c>
+      <c r="C140" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D140" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E140" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <f t="shared" si="4"/>
+        <v>134</v>
+      </c>
+      <c r="B141" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x86</v>
+      </c>
+      <c r="C141" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D141" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E141" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="B142" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x87</v>
+      </c>
+      <c r="C142" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D142" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E142" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <f t="shared" si="4"/>
+        <v>136</v>
+      </c>
+      <c r="B143" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x88</v>
+      </c>
+      <c r="C143" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D143" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E143" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <f t="shared" si="4"/>
+        <v>137</v>
+      </c>
+      <c r="B144" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x89</v>
+      </c>
+      <c r="C144" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D144" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E144" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <f t="shared" si="4"/>
+        <v>138</v>
+      </c>
+      <c r="B145" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x8A</v>
+      </c>
+      <c r="C145" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D145" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E145" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <f t="shared" si="4"/>
+        <v>139</v>
+      </c>
+      <c r="B146" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x8B</v>
+      </c>
+      <c r="C146" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D146" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E146" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <f t="shared" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="B147" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x8C</v>
+      </c>
+      <c r="C147" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D147" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E147" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <f t="shared" si="4"/>
+        <v>141</v>
+      </c>
+      <c r="B148" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x8D</v>
+      </c>
+      <c r="C148" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D148" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E148" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <f t="shared" si="4"/>
+        <v>142</v>
+      </c>
+      <c r="B149" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x8E</v>
+      </c>
+      <c r="C149" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D149" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E149" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <f t="shared" si="4"/>
+        <v>143</v>
+      </c>
+      <c r="B150" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x8F</v>
+      </c>
+      <c r="C150" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D150" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="E150" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="B151" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x90</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <f t="shared" si="4"/>
+        <v>145</v>
+      </c>
+      <c r="B152" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x91</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <f t="shared" si="4"/>
+        <v>146</v>
+      </c>
+      <c r="B153" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <f t="shared" si="4"/>
+        <v>147</v>
+      </c>
+      <c r="B154" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x93</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <f t="shared" si="4"/>
+        <v>148</v>
+      </c>
+      <c r="B155" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x94</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <f t="shared" si="4"/>
+        <v>149</v>
+      </c>
+      <c r="B156" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x95</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+      <c r="B157" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x96</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <f t="shared" si="4"/>
+        <v>151</v>
+      </c>
+      <c r="B158" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x97</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <f t="shared" si="4"/>
+        <v>152</v>
+      </c>
+      <c r="B159" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x98</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <f t="shared" si="4"/>
+        <v>153</v>
+      </c>
+      <c r="B160" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <f t="shared" si="4"/>
+        <v>154</v>
+      </c>
+      <c r="B161" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x9A</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <f t="shared" si="4"/>
+        <v>155</v>
+      </c>
+      <c r="B162" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x9B</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <f t="shared" si="4"/>
+        <v>156</v>
+      </c>
+      <c r="B163" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x9C</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <f t="shared" si="4"/>
+        <v>157</v>
+      </c>
+      <c r="B164" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x9D</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <f t="shared" si="4"/>
+        <v>158</v>
+      </c>
+      <c r="B165" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x9E</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <f t="shared" si="4"/>
+        <v>159</v>
+      </c>
+      <c r="B166" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>x9F</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="B167" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <f t="shared" si="4"/>
+        <v>161</v>
+      </c>
+      <c r="B168" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <f t="shared" si="4"/>
+        <v>162</v>
+      </c>
+      <c r="B169" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <f t="shared" si="4"/>
+        <v>163</v>
+      </c>
+      <c r="B170" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <f t="shared" si="4"/>
+        <v>164</v>
+      </c>
+      <c r="B171" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <f t="shared" si="4"/>
+        <v>165</v>
+      </c>
+      <c r="B172" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <f t="shared" si="4"/>
+        <v>166</v>
+      </c>
+      <c r="B173" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <f>A173+1</f>
+        <v>167</v>
+      </c>
+      <c r="B174" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <f t="shared" si="4"/>
+        <v>168</v>
+      </c>
+      <c r="B175" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <f t="shared" si="4"/>
+        <v>169</v>
+      </c>
+      <c r="B176" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xA9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <f t="shared" si="4"/>
+        <v>170</v>
+      </c>
+      <c r="B177" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xAA</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <f t="shared" si="4"/>
+        <v>171</v>
+      </c>
+      <c r="B178" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xAB</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <f t="shared" si="4"/>
+        <v>172</v>
+      </c>
+      <c r="B179" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xAC</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <f t="shared" si="4"/>
+        <v>173</v>
+      </c>
+      <c r="B180" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xAD</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <f t="shared" si="4"/>
+        <v>174</v>
+      </c>
+      <c r="B181" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xAE</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <f t="shared" si="4"/>
+        <v>175</v>
+      </c>
+      <c r="B182" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xAF</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <f t="shared" si="4"/>
+        <v>176</v>
+      </c>
+      <c r="B183" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <f t="shared" si="4"/>
+        <v>177</v>
+      </c>
+      <c r="B184" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <f t="shared" si="4"/>
+        <v>178</v>
+      </c>
+      <c r="B185" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <f t="shared" si="4"/>
+        <v>179</v>
+      </c>
+      <c r="B186" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <f t="shared" si="4"/>
+        <v>180</v>
+      </c>
+      <c r="B187" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <f t="shared" si="4"/>
         <v>181</v>
+      </c>
+      <c r="B188" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <f t="shared" si="4"/>
+        <v>182</v>
+      </c>
+      <c r="B189" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <f>A189+1</f>
+        <v>183</v>
+      </c>
+      <c r="B190" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <f t="shared" si="4"/>
+        <v>184</v>
+      </c>
+      <c r="B191" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+      <c r="B192" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xB9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <f t="shared" si="4"/>
+        <v>186</v>
+      </c>
+      <c r="B193" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xBA</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <f t="shared" si="4"/>
+        <v>187</v>
+      </c>
+      <c r="B194" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xBB</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <f t="shared" si="4"/>
+        <v>188</v>
+      </c>
+      <c r="B195" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xBC</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <f t="shared" si="4"/>
+        <v>189</v>
+      </c>
+      <c r="B196" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xBD</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="B197" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xBE</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <f t="shared" si="4"/>
+        <v>191</v>
+      </c>
+      <c r="B198" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xBF</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <f t="shared" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="B199" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xC0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <f t="shared" ref="A200" si="6">A199+1</f>
+        <v>193</v>
+      </c>
+      <c r="B200" s="16" t="str">
+        <f t="shared" si="5"/>
+        <v>xC1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <f>A200+1</f>
+        <v>194</v>
+      </c>
+      <c r="B201" s="16" t="str">
+        <f t="shared" ref="B201:B262" si="7">"x" &amp; DEC2HEX(A201,2)</f>
+        <v>xC2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <f t="shared" ref="A202:A214" si="8">A201+1</f>
+        <v>195</v>
+      </c>
+      <c r="B202" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <f t="shared" si="8"/>
+        <v>196</v>
+      </c>
+      <c r="B203" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <f t="shared" si="8"/>
+        <v>197</v>
+      </c>
+      <c r="B204" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <f t="shared" si="8"/>
+        <v>198</v>
+      </c>
+      <c r="B205" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <f t="shared" si="8"/>
+        <v>199</v>
+      </c>
+      <c r="B206" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <f t="shared" si="8"/>
+        <v>200</v>
+      </c>
+      <c r="B207" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <f t="shared" si="8"/>
+        <v>201</v>
+      </c>
+      <c r="B208" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xC9</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <f t="shared" si="8"/>
+        <v>202</v>
+      </c>
+      <c r="B209" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xCA</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <f t="shared" si="8"/>
+        <v>203</v>
+      </c>
+      <c r="B210" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xCB</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <f t="shared" si="8"/>
+        <v>204</v>
+      </c>
+      <c r="B211" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xCC</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <f t="shared" si="8"/>
+        <v>205</v>
+      </c>
+      <c r="B212" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xCD</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <f t="shared" si="8"/>
+        <v>206</v>
+      </c>
+      <c r="B213" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xCE</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <f t="shared" si="8"/>
+        <v>207</v>
+      </c>
+      <c r="B214" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xCF</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <f>A214+1</f>
+        <v>208</v>
+      </c>
+      <c r="B215" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <f t="shared" ref="A216:A223" si="9">A215+1</f>
+        <v>209</v>
+      </c>
+      <c r="B216" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <f t="shared" si="9"/>
+        <v>210</v>
+      </c>
+      <c r="B217" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <f t="shared" si="9"/>
+        <v>211</v>
+      </c>
+      <c r="B218" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <f t="shared" si="9"/>
+        <v>212</v>
+      </c>
+      <c r="B219" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <f t="shared" si="9"/>
+        <v>213</v>
+      </c>
+      <c r="B220" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <f t="shared" si="9"/>
+        <v>214</v>
+      </c>
+      <c r="B221" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <f t="shared" si="9"/>
+        <v>215</v>
+      </c>
+      <c r="B222" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <f t="shared" si="9"/>
+        <v>216</v>
+      </c>
+      <c r="B223" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <f>A223+1</f>
+        <v>217</v>
+      </c>
+      <c r="B224" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xD9</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <f t="shared" ref="A225:A262" si="10">A224+1</f>
+        <v>218</v>
+      </c>
+      <c r="B225" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xDA</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <f t="shared" si="10"/>
+        <v>219</v>
+      </c>
+      <c r="B226" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xDB</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <f t="shared" si="10"/>
+        <v>220</v>
+      </c>
+      <c r="B227" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xDC</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <f t="shared" si="10"/>
+        <v>221</v>
+      </c>
+      <c r="B228" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xDD</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <f t="shared" si="10"/>
+        <v>222</v>
+      </c>
+      <c r="B229" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xDE</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <f t="shared" si="10"/>
+        <v>223</v>
+      </c>
+      <c r="B230" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xDF</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <f t="shared" si="10"/>
+        <v>224</v>
+      </c>
+      <c r="B231" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <f t="shared" si="10"/>
+        <v>225</v>
+      </c>
+      <c r="B232" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <f t="shared" si="10"/>
+        <v>226</v>
+      </c>
+      <c r="B233" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <f t="shared" si="10"/>
+        <v>227</v>
+      </c>
+      <c r="B234" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <f t="shared" si="10"/>
+        <v>228</v>
+      </c>
+      <c r="B235" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <f t="shared" si="10"/>
+        <v>229</v>
+      </c>
+      <c r="B236" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <f t="shared" si="10"/>
+        <v>230</v>
+      </c>
+      <c r="B237" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <f t="shared" si="10"/>
+        <v>231</v>
+      </c>
+      <c r="B238" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <f t="shared" si="10"/>
+        <v>232</v>
+      </c>
+      <c r="B239" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <f t="shared" si="10"/>
+        <v>233</v>
+      </c>
+      <c r="B240" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xE9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <f t="shared" si="10"/>
+        <v>234</v>
+      </c>
+      <c r="B241" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xEA</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <f t="shared" si="10"/>
+        <v>235</v>
+      </c>
+      <c r="B242" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xEB</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <f t="shared" si="10"/>
+        <v>236</v>
+      </c>
+      <c r="B243" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xEC</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <f t="shared" si="10"/>
+        <v>237</v>
+      </c>
+      <c r="B244" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xED</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <f t="shared" si="10"/>
+        <v>238</v>
+      </c>
+      <c r="B245" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xEE</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <f t="shared" si="10"/>
+        <v>239</v>
+      </c>
+      <c r="B246" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xEF</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <f t="shared" si="10"/>
+        <v>240</v>
+      </c>
+      <c r="B247" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <f t="shared" si="10"/>
+        <v>241</v>
+      </c>
+      <c r="B248" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <f t="shared" si="10"/>
+        <v>242</v>
+      </c>
+      <c r="B249" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <f t="shared" si="10"/>
+        <v>243</v>
+      </c>
+      <c r="B250" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <f t="shared" si="10"/>
+        <v>244</v>
+      </c>
+      <c r="B251" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <f t="shared" si="10"/>
+        <v>245</v>
+      </c>
+      <c r="B252" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <f t="shared" si="10"/>
+        <v>246</v>
+      </c>
+      <c r="B253" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <f t="shared" si="10"/>
+        <v>247</v>
+      </c>
+      <c r="B254" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <f t="shared" si="10"/>
+        <v>248</v>
+      </c>
+      <c r="B255" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <f t="shared" si="10"/>
+        <v>249</v>
+      </c>
+      <c r="B256" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xF9</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <f t="shared" si="10"/>
+        <v>250</v>
+      </c>
+      <c r="B257" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xFA</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <f t="shared" si="10"/>
+        <v>251</v>
+      </c>
+      <c r="B258" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xFB</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <f t="shared" si="10"/>
+        <v>252</v>
+      </c>
+      <c r="B259" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xFC</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <f t="shared" si="10"/>
+        <v>253</v>
+      </c>
+      <c r="B260" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xFD</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <f t="shared" si="10"/>
+        <v>254</v>
+      </c>
+      <c r="B261" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xFE</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <f t="shared" si="10"/>
+        <v>255</v>
+      </c>
+      <c r="B262" s="16" t="str">
+        <f t="shared" si="7"/>
+        <v>xFF</v>
       </c>
     </row>
   </sheetData>
@@ -3441,4 +5034,2225 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91517B1F-406D-4F65-BBD5-9E59DD7F84C2}">
+  <dimension ref="A1:F139"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>B2</f>
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f t="shared" ref="A4:A69" si="0">A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B2+1</f>
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f>A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>B4+1</f>
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f>A6+1</f>
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>B6</f>
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f>A7+1</f>
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>B6+1</f>
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>B8</f>
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f t="shared" ref="B10" si="1">B8+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f t="shared" ref="B11" si="2">B10</f>
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12" si="3">B10+1</f>
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13" si="4">B12</f>
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <f t="shared" ref="B14" si="5">B12+1</f>
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <f t="shared" ref="B15" si="6">B14</f>
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16" si="7">B14+1</f>
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <f t="shared" ref="B17" si="8">B16</f>
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <f t="shared" ref="B18" si="9">B16+1</f>
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <f t="shared" ref="B19" si="10">B18</f>
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <f t="shared" ref="B20" si="11">B18+1</f>
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <f t="shared" ref="B21" si="12">B20</f>
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <f t="shared" ref="B22" si="13">B20+1</f>
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <f t="shared" ref="B23" si="14">B22</f>
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <f t="shared" ref="B24" si="15">B22+1</f>
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25" si="16">B24</f>
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ref="B26" si="17">B24+1</f>
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <f t="shared" ref="B27" si="18">B26</f>
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ref="B28" si="19">B26+1</f>
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ref="B29" si="20">B28</f>
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <f t="shared" ref="B30" si="21">B28+1</f>
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <f t="shared" ref="B31" si="22">B30</f>
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <f t="shared" ref="B32" si="23">B30+1</f>
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <f t="shared" ref="B33" si="24">B32</f>
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>196</v>
+      </c>
+      <c r="D33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <f t="shared" ref="B34" si="25">B32+1</f>
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>197</v>
+      </c>
+      <c r="D34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <f t="shared" ref="B35" si="26">B34</f>
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <f t="shared" ref="B36" si="27">B34+1</f>
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <f t="shared" ref="B37" si="28">B36</f>
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <f t="shared" ref="B38" si="29">B36+1</f>
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>222</v>
+      </c>
+      <c r="D38" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <f t="shared" ref="B39" si="30">B38</f>
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <f t="shared" ref="B40" si="31">B38+1</f>
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <f t="shared" ref="B41" si="32">B40</f>
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ref="B42" si="33">B40+1</f>
+        <v>20</v>
+      </c>
+      <c r="C42" t="s">
+        <v>209</v>
+      </c>
+      <c r="D42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <f t="shared" ref="B43" si="34">B42</f>
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <f t="shared" ref="B44" si="35">B42+1</f>
+        <v>21</v>
+      </c>
+      <c r="C44" t="s">
+        <v>211</v>
+      </c>
+      <c r="D44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <f t="shared" ref="B45" si="36">B44</f>
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <f t="shared" ref="B46" si="37">B44+1</f>
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <f t="shared" ref="B47" si="38">B46</f>
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <f t="shared" ref="B48" si="39">B46+1</f>
+        <v>23</v>
+      </c>
+      <c r="C48" t="s">
+        <v>215</v>
+      </c>
+      <c r="D48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <f t="shared" ref="B49" si="40">B48</f>
+        <v>23</v>
+      </c>
+      <c r="C49" t="s">
+        <v>216</v>
+      </c>
+      <c r="D49" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <f t="shared" ref="B50" si="41">B48+1</f>
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>217</v>
+      </c>
+      <c r="D50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <f t="shared" ref="B51" si="42">B50</f>
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <f t="shared" ref="B52" si="43">B50+1</f>
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>219</v>
+      </c>
+      <c r="D52" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <f t="shared" ref="B53" si="44">B52</f>
+        <v>25</v>
+      </c>
+      <c r="C53" t="s">
+        <v>220</v>
+      </c>
+      <c r="D53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <f t="shared" ref="B54" si="45">B52+1</f>
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>221</v>
+      </c>
+      <c r="D54" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <f t="shared" ref="B55" si="46">B54</f>
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>227</v>
+      </c>
+      <c r="D55" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <f t="shared" ref="B56" si="47">B54+1</f>
+        <v>27</v>
+      </c>
+      <c r="C56" t="s">
+        <v>223</v>
+      </c>
+      <c r="D56" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <f t="shared" ref="B57" si="48">B56</f>
+        <v>27</v>
+      </c>
+      <c r="C57" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <f t="shared" ref="B58" si="49">B56+1</f>
+        <v>28</v>
+      </c>
+      <c r="C58" t="s">
+        <v>225</v>
+      </c>
+      <c r="D58" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <f t="shared" ref="B59" si="50">B58</f>
+        <v>28</v>
+      </c>
+      <c r="C59" t="s">
+        <v>226</v>
+      </c>
+      <c r="D59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <f t="shared" ref="B60" si="51">B58+1</f>
+        <v>29</v>
+      </c>
+      <c r="C60" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <f t="shared" ref="B61" si="52">B60</f>
+        <v>29</v>
+      </c>
+      <c r="C61" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <f t="shared" ref="B62" si="53">B60+1</f>
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>237</v>
+      </c>
+      <c r="D62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <f t="shared" ref="B63" si="54">B62</f>
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <f t="shared" ref="B64" si="55">B62+1</f>
+        <v>31</v>
+      </c>
+      <c r="C64" t="s">
+        <v>235</v>
+      </c>
+      <c r="D64" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <f t="shared" ref="B65" si="56">B64</f>
+        <v>31</v>
+      </c>
+      <c r="C65" t="s">
+        <v>234</v>
+      </c>
+      <c r="D65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <f t="shared" ref="B66" si="57">B64+1</f>
+        <v>32</v>
+      </c>
+      <c r="C66" t="s">
+        <v>233</v>
+      </c>
+      <c r="D66" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <f t="shared" ref="B67" si="58">B66</f>
+        <v>32</v>
+      </c>
+      <c r="C67" t="s">
+        <v>232</v>
+      </c>
+      <c r="D67" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <f t="shared" ref="B68" si="59">B66+1</f>
+        <v>33</v>
+      </c>
+      <c r="C68" t="s">
+        <v>231</v>
+      </c>
+      <c r="D68" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <f t="shared" ref="B69" si="60">B68</f>
+        <v>33</v>
+      </c>
+      <c r="C69" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <f t="shared" ref="A70:A133" si="61">A69+1</f>
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <f t="shared" ref="B70" si="62">B68+1</f>
+        <v>34</v>
+      </c>
+      <c r="C70" t="s">
+        <v>229</v>
+      </c>
+      <c r="D70" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f t="shared" si="61"/>
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <f t="shared" ref="B71" si="63">B70</f>
+        <v>34</v>
+      </c>
+      <c r="C71" t="s">
+        <v>228</v>
+      </c>
+      <c r="D71" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <f t="shared" si="61"/>
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <f t="shared" ref="B72" si="64">B70+1</f>
+        <v>35</v>
+      </c>
+      <c r="C72" t="s">
+        <v>222</v>
+      </c>
+      <c r="D72" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <f t="shared" si="61"/>
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <f t="shared" ref="B73" si="65">B72</f>
+        <v>35</v>
+      </c>
+      <c r="C73" t="s">
+        <v>206</v>
+      </c>
+      <c r="D73" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <f t="shared" si="61"/>
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <f t="shared" ref="B74" si="66">B72+1</f>
+        <v>36</v>
+      </c>
+      <c r="C74" t="s">
+        <v>207</v>
+      </c>
+      <c r="D74" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <f t="shared" si="61"/>
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <f t="shared" ref="B75" si="67">B74</f>
+        <v>36</v>
+      </c>
+      <c r="C75" t="s">
+        <v>208</v>
+      </c>
+      <c r="D75" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <f t="shared" si="61"/>
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <f t="shared" ref="B76" si="68">B74+1</f>
+        <v>37</v>
+      </c>
+      <c r="C76" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <f t="shared" si="61"/>
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <f t="shared" ref="B77" si="69">B76</f>
+        <v>37</v>
+      </c>
+      <c r="C77" t="s">
+        <v>210</v>
+      </c>
+      <c r="D77" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <f t="shared" si="61"/>
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <f t="shared" ref="B78" si="70">B76+1</f>
+        <v>38</v>
+      </c>
+      <c r="C78" t="s">
+        <v>211</v>
+      </c>
+      <c r="D78" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <f t="shared" si="61"/>
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <f t="shared" ref="B79" si="71">B78</f>
+        <v>38</v>
+      </c>
+      <c r="C79" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <f t="shared" si="61"/>
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <f t="shared" ref="B80" si="72">B78+1</f>
+        <v>39</v>
+      </c>
+      <c r="C80" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <f t="shared" si="61"/>
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <f t="shared" ref="B81" si="73">B80</f>
+        <v>39</v>
+      </c>
+      <c r="C81" t="s">
+        <v>214</v>
+      </c>
+      <c r="D81" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <f t="shared" si="61"/>
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <f t="shared" ref="B82" si="74">B80+1</f>
+        <v>40</v>
+      </c>
+      <c r="C82" t="s">
+        <v>215</v>
+      </c>
+      <c r="D82" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <f t="shared" si="61"/>
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <f t="shared" ref="B83" si="75">B82</f>
+        <v>40</v>
+      </c>
+      <c r="C83" t="s">
+        <v>216</v>
+      </c>
+      <c r="D83" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <f t="shared" si="61"/>
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <f t="shared" ref="B84" si="76">B82+1</f>
+        <v>41</v>
+      </c>
+      <c r="C84" t="s">
+        <v>217</v>
+      </c>
+      <c r="D84" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <f t="shared" si="61"/>
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <f t="shared" ref="B85" si="77">B84</f>
+        <v>41</v>
+      </c>
+      <c r="C85" t="s">
+        <v>218</v>
+      </c>
+      <c r="D85" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <f t="shared" si="61"/>
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <f t="shared" ref="B86" si="78">B84+1</f>
+        <v>42</v>
+      </c>
+      <c r="C86" t="s">
+        <v>219</v>
+      </c>
+      <c r="D86" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <f t="shared" si="61"/>
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <f t="shared" ref="B87" si="79">B86</f>
+        <v>42</v>
+      </c>
+      <c r="C87" t="s">
+        <v>220</v>
+      </c>
+      <c r="D87" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <f t="shared" si="61"/>
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <f t="shared" ref="B88" si="80">B86+1</f>
+        <v>43</v>
+      </c>
+      <c r="C88" t="s">
+        <v>221</v>
+      </c>
+      <c r="D88" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <f t="shared" si="61"/>
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <f t="shared" ref="B89" si="81">B88</f>
+        <v>43</v>
+      </c>
+      <c r="C89" t="s">
+        <v>227</v>
+      </c>
+      <c r="D89" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <f t="shared" si="61"/>
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <f t="shared" ref="B90" si="82">B88+1</f>
+        <v>44</v>
+      </c>
+      <c r="C90" t="s">
+        <v>223</v>
+      </c>
+      <c r="D90" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <f t="shared" si="61"/>
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <f t="shared" ref="B91" si="83">B90</f>
+        <v>44</v>
+      </c>
+      <c r="C91" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <f t="shared" si="61"/>
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <f t="shared" ref="B92" si="84">B90+1</f>
+        <v>45</v>
+      </c>
+      <c r="C92" t="s">
+        <v>225</v>
+      </c>
+      <c r="D92" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <f t="shared" si="61"/>
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <f t="shared" ref="B93" si="85">B92</f>
+        <v>45</v>
+      </c>
+      <c r="C93" t="s">
+        <v>226</v>
+      </c>
+      <c r="D93" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <f t="shared" si="61"/>
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <f t="shared" ref="B94" si="86">B92+1</f>
+        <v>46</v>
+      </c>
+      <c r="C94" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <f t="shared" si="61"/>
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <f t="shared" ref="B95" si="87">B94</f>
+        <v>46</v>
+      </c>
+      <c r="C95" t="s">
+        <v>238</v>
+      </c>
+      <c r="D95" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <f t="shared" si="61"/>
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <f t="shared" ref="B96" si="88">B94+1</f>
+        <v>47</v>
+      </c>
+      <c r="C96" t="s">
+        <v>237</v>
+      </c>
+      <c r="D96" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <f t="shared" si="61"/>
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <f t="shared" ref="B97" si="89">B96</f>
+        <v>47</v>
+      </c>
+      <c r="C97" t="s">
+        <v>236</v>
+      </c>
+      <c r="D97" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <f t="shared" si="61"/>
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <f t="shared" ref="B98" si="90">B96+1</f>
+        <v>48</v>
+      </c>
+      <c r="C98" t="s">
+        <v>235</v>
+      </c>
+      <c r="D98" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <f t="shared" si="61"/>
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <f t="shared" ref="B99" si="91">B98</f>
+        <v>48</v>
+      </c>
+      <c r="C99" t="s">
+        <v>234</v>
+      </c>
+      <c r="D99" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <f t="shared" si="61"/>
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <f t="shared" ref="B100" si="92">B98+1</f>
+        <v>49</v>
+      </c>
+      <c r="C100" t="s">
+        <v>233</v>
+      </c>
+      <c r="D100" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <f t="shared" si="61"/>
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <f t="shared" ref="B101" si="93">B100</f>
+        <v>49</v>
+      </c>
+      <c r="C101" t="s">
+        <v>232</v>
+      </c>
+      <c r="D101" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <f t="shared" si="61"/>
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <f t="shared" ref="B102" si="94">B100+1</f>
+        <v>50</v>
+      </c>
+      <c r="C102" t="s">
+        <v>231</v>
+      </c>
+      <c r="D102" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <f t="shared" si="61"/>
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <f t="shared" ref="B103" si="95">B102</f>
+        <v>50</v>
+      </c>
+      <c r="C103" t="s">
+        <v>230</v>
+      </c>
+      <c r="D103" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <f t="shared" si="61"/>
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <f t="shared" ref="B104" si="96">B102+1</f>
+        <v>51</v>
+      </c>
+      <c r="C104" t="s">
+        <v>229</v>
+      </c>
+      <c r="D104" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <f t="shared" si="61"/>
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <f t="shared" ref="B105" si="97">B104</f>
+        <v>51</v>
+      </c>
+      <c r="C105" t="s">
+        <v>228</v>
+      </c>
+      <c r="D105" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <f t="shared" si="61"/>
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <f t="shared" ref="B106" si="98">B104+1</f>
+        <v>52</v>
+      </c>
+      <c r="C106" t="s">
+        <v>222</v>
+      </c>
+      <c r="D106" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <f t="shared" si="61"/>
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <f t="shared" ref="B107" si="99">B106</f>
+        <v>52</v>
+      </c>
+      <c r="C107" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <f t="shared" si="61"/>
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <f t="shared" ref="B108" si="100">B106+1</f>
+        <v>53</v>
+      </c>
+      <c r="C108" t="s">
+        <v>207</v>
+      </c>
+      <c r="D108" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <f t="shared" si="61"/>
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <f t="shared" ref="B109" si="101">B108</f>
+        <v>53</v>
+      </c>
+      <c r="C109" t="s">
+        <v>208</v>
+      </c>
+      <c r="D109" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <f t="shared" si="61"/>
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <f t="shared" ref="B110" si="102">B108+1</f>
+        <v>54</v>
+      </c>
+      <c r="C110" t="s">
+        <v>209</v>
+      </c>
+      <c r="D110" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <f t="shared" si="61"/>
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <f t="shared" ref="B111" si="103">B110</f>
+        <v>54</v>
+      </c>
+      <c r="C111" t="s">
+        <v>210</v>
+      </c>
+      <c r="D111" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <f t="shared" si="61"/>
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <f t="shared" ref="B112" si="104">B110+1</f>
+        <v>55</v>
+      </c>
+      <c r="C112" t="s">
+        <v>211</v>
+      </c>
+      <c r="D112" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <f t="shared" si="61"/>
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <f t="shared" ref="B113" si="105">B112</f>
+        <v>55</v>
+      </c>
+      <c r="C113" t="s">
+        <v>212</v>
+      </c>
+      <c r="D113" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <f t="shared" si="61"/>
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <f t="shared" ref="B114" si="106">B112+1</f>
+        <v>56</v>
+      </c>
+      <c r="C114" t="s">
+        <v>213</v>
+      </c>
+      <c r="D114" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <f t="shared" si="61"/>
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <f t="shared" ref="B115" si="107">B114</f>
+        <v>56</v>
+      </c>
+      <c r="C115" t="s">
+        <v>214</v>
+      </c>
+      <c r="D115" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <f t="shared" si="61"/>
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <f t="shared" ref="B116" si="108">B114+1</f>
+        <v>57</v>
+      </c>
+      <c r="C116" t="s">
+        <v>215</v>
+      </c>
+      <c r="D116" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <f t="shared" si="61"/>
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <f t="shared" ref="B117" si="109">B116</f>
+        <v>57</v>
+      </c>
+      <c r="C117" t="s">
+        <v>216</v>
+      </c>
+      <c r="D117" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <f t="shared" si="61"/>
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <f t="shared" ref="B118" si="110">B116+1</f>
+        <v>58</v>
+      </c>
+      <c r="C118" t="s">
+        <v>217</v>
+      </c>
+      <c r="D118" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <f t="shared" si="61"/>
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <f t="shared" ref="B119" si="111">B118</f>
+        <v>58</v>
+      </c>
+      <c r="C119" t="s">
+        <v>218</v>
+      </c>
+      <c r="D119" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <f t="shared" si="61"/>
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <f t="shared" ref="B120" si="112">B118+1</f>
+        <v>59</v>
+      </c>
+      <c r="C120" t="s">
+        <v>219</v>
+      </c>
+      <c r="D120" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <f t="shared" si="61"/>
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <f t="shared" ref="B121" si="113">B120</f>
+        <v>59</v>
+      </c>
+      <c r="C121" t="s">
+        <v>220</v>
+      </c>
+      <c r="D121" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <f t="shared" si="61"/>
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <f t="shared" ref="B122" si="114">B120+1</f>
+        <v>60</v>
+      </c>
+      <c r="C122" t="s">
+        <v>221</v>
+      </c>
+      <c r="D122" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <f t="shared" si="61"/>
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <f t="shared" ref="B123" si="115">B122</f>
+        <v>60</v>
+      </c>
+      <c r="C123" t="s">
+        <v>227</v>
+      </c>
+      <c r="D123" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <f t="shared" si="61"/>
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <f t="shared" ref="B124" si="116">B122+1</f>
+        <v>61</v>
+      </c>
+      <c r="C124" t="s">
+        <v>223</v>
+      </c>
+      <c r="D124" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <f t="shared" si="61"/>
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <f t="shared" ref="B125" si="117">B124</f>
+        <v>61</v>
+      </c>
+      <c r="C125" t="s">
+        <v>224</v>
+      </c>
+      <c r="D125" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <f t="shared" si="61"/>
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <f t="shared" ref="B126" si="118">B124+1</f>
+        <v>62</v>
+      </c>
+      <c r="C126" t="s">
+        <v>225</v>
+      </c>
+      <c r="D126" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <f t="shared" si="61"/>
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <f t="shared" ref="B127" si="119">B126</f>
+        <v>62</v>
+      </c>
+      <c r="C127" t="s">
+        <v>226</v>
+      </c>
+      <c r="D127" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <f t="shared" si="61"/>
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <f t="shared" ref="B128" si="120">B126+1</f>
+        <v>63</v>
+      </c>
+      <c r="C128" t="s">
+        <v>239</v>
+      </c>
+      <c r="D128" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <f t="shared" si="61"/>
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <f t="shared" ref="B129" si="121">B128</f>
+        <v>63</v>
+      </c>
+      <c r="C129" t="s">
+        <v>238</v>
+      </c>
+      <c r="D129" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <f t="shared" si="61"/>
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <f t="shared" ref="B130" si="122">B128+1</f>
+        <v>64</v>
+      </c>
+      <c r="C130" t="s">
+        <v>237</v>
+      </c>
+      <c r="D130" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <f t="shared" si="61"/>
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <f t="shared" ref="B131" si="123">B130</f>
+        <v>64</v>
+      </c>
+      <c r="C131" t="s">
+        <v>236</v>
+      </c>
+      <c r="D131" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <f t="shared" si="61"/>
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <f t="shared" ref="B132" si="124">B130+1</f>
+        <v>65</v>
+      </c>
+      <c r="C132" t="s">
+        <v>235</v>
+      </c>
+      <c r="D132" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <f t="shared" si="61"/>
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <f t="shared" ref="B133" si="125">B132</f>
+        <v>65</v>
+      </c>
+      <c r="C133" t="s">
+        <v>234</v>
+      </c>
+      <c r="D133" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <f t="shared" ref="A134:A139" si="126">A133+1</f>
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <f t="shared" ref="B134" si="127">B132+1</f>
+        <v>66</v>
+      </c>
+      <c r="C134" t="s">
+        <v>233</v>
+      </c>
+      <c r="D134" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <f t="shared" si="126"/>
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <f t="shared" ref="B135" si="128">B134</f>
+        <v>66</v>
+      </c>
+      <c r="C135" t="s">
+        <v>232</v>
+      </c>
+      <c r="D135" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <f t="shared" si="126"/>
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <f>B134+1</f>
+        <v>67</v>
+      </c>
+      <c r="C136" t="s">
+        <v>231</v>
+      </c>
+      <c r="D136" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <f t="shared" si="126"/>
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <f t="shared" ref="B137:B139" si="129">B136</f>
+        <v>67</v>
+      </c>
+      <c r="C137" t="s">
+        <v>230</v>
+      </c>
+      <c r="D137" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <f t="shared" si="126"/>
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <f>B137+1</f>
+        <v>68</v>
+      </c>
+      <c r="C138" t="s">
+        <v>229</v>
+      </c>
+      <c r="D138" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <f t="shared" si="126"/>
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <f t="shared" si="129"/>
+        <v>68</v>
+      </c>
+      <c r="C139" t="s">
+        <v>228</v>
+      </c>
+      <c r="D139" t="s">
+        <v>204</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\clean\FLOWER-BOARD-Firmware\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\dev\FLOWER-board-firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B20BF66-5D7C-4842-8203-FA81531C5763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69701C28-00A0-4286-996E-2D1F345790AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registers" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="247">
   <si>
     <t>Register Map</t>
   </si>
@@ -684,27 +684,6 @@
     <t>Beam 8 Trigger</t>
   </si>
   <si>
-    <t>Beam 9 Trigger</t>
-  </si>
-  <si>
-    <t>Beam 10 Trigger</t>
-  </si>
-  <si>
-    <t>Beam 11 Trigger</t>
-  </si>
-  <si>
-    <t>Beam 12 Trigger</t>
-  </si>
-  <si>
-    <t>Beam 13 Trigger</t>
-  </si>
-  <si>
-    <t>Beam 14 Trigger</t>
-  </si>
-  <si>
-    <t>Beam 15 Trigger</t>
-  </si>
-  <si>
     <t>Phased Trigger</t>
   </si>
   <si>
@@ -721,27 +700,6 @@
   </si>
   <si>
     <t>Phased Servo</t>
-  </si>
-  <si>
-    <t>Beam 15 Servo</t>
-  </si>
-  <si>
-    <t>Beam 14 Servo</t>
-  </si>
-  <si>
-    <t>Beam 13 Servo</t>
-  </si>
-  <si>
-    <t>Beam 12 Servo</t>
-  </si>
-  <si>
-    <t>Beam 11 Servo</t>
-  </si>
-  <si>
-    <t>Beam 10 Servo</t>
-  </si>
-  <si>
-    <t>Beam 9 Servo</t>
   </si>
   <si>
     <t>Beam 8 Servo</t>
@@ -1799,7 +1757,7 @@
         <v>182</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -1819,7 +1777,7 @@
         <v>183</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -2137,7 +2095,7 @@
         <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
@@ -2775,10 +2733,10 @@
         <v>x50</v>
       </c>
       <c r="C87" s="42" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D87" s="43" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="E87" s="42" t="s">
         <v>48</v>
@@ -2797,16 +2755,16 @@
         <v>x51</v>
       </c>
       <c r="C88" s="42" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D88" s="43" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="E88" s="42" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F88" s="43" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2991,7 +2949,7 @@
         <v>x5B</v>
       </c>
       <c r="C98" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>155</v>
@@ -3610,13 +3568,13 @@
         <v>x80</v>
       </c>
       <c r="C135" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D135" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E135" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -3629,13 +3587,13 @@
         <v>x81</v>
       </c>
       <c r="C136" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D136" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E136" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -3648,13 +3606,13 @@
         <v>x82</v>
       </c>
       <c r="C137" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D137" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E137" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -3667,13 +3625,13 @@
         <v>x83</v>
       </c>
       <c r="C138" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D138" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E138" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -3686,13 +3644,13 @@
         <v>x84</v>
       </c>
       <c r="C139" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D139" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E139" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -3705,13 +3663,13 @@
         <v>x85</v>
       </c>
       <c r="C140" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D140" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E140" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -3724,13 +3682,13 @@
         <v>x86</v>
       </c>
       <c r="C141" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D141" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E141" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -3743,13 +3701,13 @@
         <v>x87</v>
       </c>
       <c r="C142" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D142" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E142" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -3762,13 +3720,13 @@
         <v>x88</v>
       </c>
       <c r="C143" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D143" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E143" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -3781,13 +3739,13 @@
         <v>x89</v>
       </c>
       <c r="C144" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D144" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E144" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -3800,13 +3758,13 @@
         <v>x8A</v>
       </c>
       <c r="C145" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D145" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E145" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -3819,13 +3777,13 @@
         <v>x8B</v>
       </c>
       <c r="C146" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D146" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E146" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -3838,13 +3796,13 @@
         <v>x8C</v>
       </c>
       <c r="C147" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D147" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E147" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -3857,13 +3815,13 @@
         <v>x8D</v>
       </c>
       <c r="C148" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D148" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E148" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -3876,13 +3834,13 @@
         <v>x8E</v>
       </c>
       <c r="C149" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D149" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E149" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -3895,13 +3853,13 @@
         <v>x8F</v>
       </c>
       <c r="C150" s="40" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D150" s="40" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E150" s="40" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -5038,7 +4996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91517B1F-406D-4F65-BBD5-9E59DD7F84C2}">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -5052,16 +5010,16 @@
         <v>201</v>
       </c>
       <c r="B1" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>202</v>
       </c>
       <c r="D1" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="F1" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -5072,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -5098,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -5111,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -5124,7 +5082,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -5137,7 +5095,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -5630,7 +5588,7 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D38" t="s">
         <v>190</v>
@@ -5790,7 +5748,7 @@
         <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D48" t="s">
         <v>190</v>
@@ -5870,7 +5828,7 @@
         <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D53" t="s">
         <v>190</v>
@@ -5886,7 +5844,7 @@
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D54" t="s">
         <v>190</v>
@@ -5902,7 +5860,7 @@
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D55" t="s">
         <v>190</v>
@@ -5918,7 +5876,7 @@
         <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D56" t="s">
         <v>190</v>
@@ -5934,7 +5892,7 @@
         <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D57" t="s">
         <v>190</v>
@@ -5950,10 +5908,10 @@
         <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D58" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -5966,10 +5924,10 @@
         <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D59" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -5982,10 +5940,10 @@
         <v>29</v>
       </c>
       <c r="C60" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D60" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -5998,10 +5956,10 @@
         <v>29</v>
       </c>
       <c r="C61" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="D61" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -6014,10 +5972,10 @@
         <v>30</v>
       </c>
       <c r="C62" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="D62" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -6030,10 +5988,10 @@
         <v>30</v>
       </c>
       <c r="C63" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="D63" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -6046,10 +6004,10 @@
         <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D64" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -6062,10 +6020,10 @@
         <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -6078,10 +6036,10 @@
         <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="D66" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -6094,10 +6052,10 @@
         <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D67" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -6110,10 +6068,10 @@
         <v>33</v>
       </c>
       <c r="C68" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D68" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -6126,10 +6084,10 @@
         <v>33</v>
       </c>
       <c r="C69" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D69" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -6142,10 +6100,10 @@
         <v>34</v>
       </c>
       <c r="C70" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D70" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -6158,10 +6116,10 @@
         <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D71" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -6174,7 +6132,7 @@
         <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D72" t="s">
         <v>203</v>
@@ -6190,7 +6148,7 @@
         <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="D73" t="s">
         <v>203</v>
@@ -6206,7 +6164,7 @@
         <v>36</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="D74" t="s">
         <v>203</v>
@@ -6222,7 +6180,7 @@
         <v>36</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D75" t="s">
         <v>203</v>
@@ -6238,7 +6196,7 @@
         <v>37</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="D76" t="s">
         <v>203</v>
@@ -6254,7 +6212,7 @@
         <v>37</v>
       </c>
       <c r="C77" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D77" t="s">
         <v>203</v>
@@ -6270,10 +6228,10 @@
         <v>38</v>
       </c>
       <c r="C78" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -6286,10 +6244,10 @@
         <v>38</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -6302,10 +6260,10 @@
         <v>39</v>
       </c>
       <c r="C80" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -6318,10 +6276,10 @@
         <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -6334,10 +6292,10 @@
         <v>40</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D82" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -6350,10 +6308,10 @@
         <v>40</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D83" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -6366,10 +6324,10 @@
         <v>41</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -6382,10 +6340,10 @@
         <v>41</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D85" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -6398,10 +6356,10 @@
         <v>42</v>
       </c>
       <c r="C86" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D86" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -6414,10 +6372,10 @@
         <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -6430,10 +6388,10 @@
         <v>43</v>
       </c>
       <c r="C88" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D88" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -6446,10 +6404,10 @@
         <v>43</v>
       </c>
       <c r="C89" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D89" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -6462,10 +6420,10 @@
         <v>44</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -6478,10 +6436,10 @@
         <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -6494,10 +6452,10 @@
         <v>45</v>
       </c>
       <c r="C92" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -6510,10 +6468,10 @@
         <v>45</v>
       </c>
       <c r="C93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -6526,10 +6484,10 @@
         <v>46</v>
       </c>
       <c r="C94" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D94" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -6542,10 +6500,10 @@
         <v>46</v>
       </c>
       <c r="C95" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -6558,10 +6516,10 @@
         <v>47</v>
       </c>
       <c r="C96" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D96" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -6574,681 +6532,9 @@
         <v>47</v>
       </c>
       <c r="C97" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D97" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <f t="shared" si="61"/>
-        <v>96</v>
-      </c>
-      <c r="B98">
-        <f t="shared" ref="B98" si="90">B96+1</f>
-        <v>48</v>
-      </c>
-      <c r="C98" t="s">
-        <v>235</v>
-      </c>
-      <c r="D98" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <f t="shared" si="61"/>
-        <v>97</v>
-      </c>
-      <c r="B99">
-        <f t="shared" ref="B99" si="91">B98</f>
-        <v>48</v>
-      </c>
-      <c r="C99" t="s">
-        <v>234</v>
-      </c>
-      <c r="D99" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <f t="shared" si="61"/>
-        <v>98</v>
-      </c>
-      <c r="B100">
-        <f t="shared" ref="B100" si="92">B98+1</f>
-        <v>49</v>
-      </c>
-      <c r="C100" t="s">
-        <v>233</v>
-      </c>
-      <c r="D100" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <f t="shared" si="61"/>
-        <v>99</v>
-      </c>
-      <c r="B101">
-        <f t="shared" ref="B101" si="93">B100</f>
-        <v>49</v>
-      </c>
-      <c r="C101" t="s">
-        <v>232</v>
-      </c>
-      <c r="D101" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <f t="shared" si="61"/>
-        <v>100</v>
-      </c>
-      <c r="B102">
-        <f t="shared" ref="B102" si="94">B100+1</f>
-        <v>50</v>
-      </c>
-      <c r="C102" t="s">
-        <v>231</v>
-      </c>
-      <c r="D102" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <f t="shared" si="61"/>
-        <v>101</v>
-      </c>
-      <c r="B103">
-        <f t="shared" ref="B103" si="95">B102</f>
-        <v>50</v>
-      </c>
-      <c r="C103" t="s">
-        <v>230</v>
-      </c>
-      <c r="D103" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <f t="shared" si="61"/>
-        <v>102</v>
-      </c>
-      <c r="B104">
-        <f t="shared" ref="B104" si="96">B102+1</f>
-        <v>51</v>
-      </c>
-      <c r="C104" t="s">
-        <v>229</v>
-      </c>
-      <c r="D104" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <f t="shared" si="61"/>
-        <v>103</v>
-      </c>
-      <c r="B105">
-        <f t="shared" ref="B105" si="97">B104</f>
-        <v>51</v>
-      </c>
-      <c r="C105" t="s">
-        <v>228</v>
-      </c>
-      <c r="D105" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <f t="shared" si="61"/>
-        <v>104</v>
-      </c>
-      <c r="B106">
-        <f t="shared" ref="B106" si="98">B104+1</f>
-        <v>52</v>
-      </c>
-      <c r="C106" t="s">
-        <v>222</v>
-      </c>
-      <c r="D106" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <f t="shared" si="61"/>
-        <v>105</v>
-      </c>
-      <c r="B107">
-        <f t="shared" ref="B107" si="99">B106</f>
-        <v>52</v>
-      </c>
-      <c r="C107" t="s">
-        <v>206</v>
-      </c>
-      <c r="D107" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <f t="shared" si="61"/>
-        <v>106</v>
-      </c>
-      <c r="B108">
-        <f t="shared" ref="B108" si="100">B106+1</f>
-        <v>53</v>
-      </c>
-      <c r="C108" t="s">
-        <v>207</v>
-      </c>
-      <c r="D108" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <f t="shared" si="61"/>
-        <v>107</v>
-      </c>
-      <c r="B109">
-        <f t="shared" ref="B109" si="101">B108</f>
-        <v>53</v>
-      </c>
-      <c r="C109" t="s">
-        <v>208</v>
-      </c>
-      <c r="D109" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <f t="shared" si="61"/>
-        <v>108</v>
-      </c>
-      <c r="B110">
-        <f t="shared" ref="B110" si="102">B108+1</f>
-        <v>54</v>
-      </c>
-      <c r="C110" t="s">
-        <v>209</v>
-      </c>
-      <c r="D110" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <f t="shared" si="61"/>
-        <v>109</v>
-      </c>
-      <c r="B111">
-        <f t="shared" ref="B111" si="103">B110</f>
-        <v>54</v>
-      </c>
-      <c r="C111" t="s">
-        <v>210</v>
-      </c>
-      <c r="D111" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <f t="shared" si="61"/>
-        <v>110</v>
-      </c>
-      <c r="B112">
-        <f t="shared" ref="B112" si="104">B110+1</f>
-        <v>55</v>
-      </c>
-      <c r="C112" t="s">
-        <v>211</v>
-      </c>
-      <c r="D112" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <f t="shared" si="61"/>
-        <v>111</v>
-      </c>
-      <c r="B113">
-        <f t="shared" ref="B113" si="105">B112</f>
-        <v>55</v>
-      </c>
-      <c r="C113" t="s">
-        <v>212</v>
-      </c>
-      <c r="D113" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <f t="shared" si="61"/>
-        <v>112</v>
-      </c>
-      <c r="B114">
-        <f t="shared" ref="B114" si="106">B112+1</f>
-        <v>56</v>
-      </c>
-      <c r="C114" t="s">
-        <v>213</v>
-      </c>
-      <c r="D114" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <f t="shared" si="61"/>
-        <v>113</v>
-      </c>
-      <c r="B115">
-        <f t="shared" ref="B115" si="107">B114</f>
-        <v>56</v>
-      </c>
-      <c r="C115" t="s">
-        <v>214</v>
-      </c>
-      <c r="D115" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <f t="shared" si="61"/>
-        <v>114</v>
-      </c>
-      <c r="B116">
-        <f t="shared" ref="B116" si="108">B114+1</f>
-        <v>57</v>
-      </c>
-      <c r="C116" t="s">
-        <v>215</v>
-      </c>
-      <c r="D116" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <f t="shared" si="61"/>
-        <v>115</v>
-      </c>
-      <c r="B117">
-        <f t="shared" ref="B117" si="109">B116</f>
-        <v>57</v>
-      </c>
-      <c r="C117" t="s">
-        <v>216</v>
-      </c>
-      <c r="D117" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118">
-        <f t="shared" si="61"/>
-        <v>116</v>
-      </c>
-      <c r="B118">
-        <f t="shared" ref="B118" si="110">B116+1</f>
-        <v>58</v>
-      </c>
-      <c r="C118" t="s">
-        <v>217</v>
-      </c>
-      <c r="D118" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119">
-        <f t="shared" si="61"/>
-        <v>117</v>
-      </c>
-      <c r="B119">
-        <f t="shared" ref="B119" si="111">B118</f>
-        <v>58</v>
-      </c>
-      <c r="C119" t="s">
-        <v>218</v>
-      </c>
-      <c r="D119" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120">
-        <f t="shared" si="61"/>
-        <v>118</v>
-      </c>
-      <c r="B120">
-        <f t="shared" ref="B120" si="112">B118+1</f>
-        <v>59</v>
-      </c>
-      <c r="C120" t="s">
-        <v>219</v>
-      </c>
-      <c r="D120" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <f t="shared" si="61"/>
-        <v>119</v>
-      </c>
-      <c r="B121">
-        <f t="shared" ref="B121" si="113">B120</f>
-        <v>59</v>
-      </c>
-      <c r="C121" t="s">
-        <v>220</v>
-      </c>
-      <c r="D121" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <f t="shared" si="61"/>
-        <v>120</v>
-      </c>
-      <c r="B122">
-        <f t="shared" ref="B122" si="114">B120+1</f>
-        <v>60</v>
-      </c>
-      <c r="C122" t="s">
-        <v>221</v>
-      </c>
-      <c r="D122" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <f t="shared" si="61"/>
-        <v>121</v>
-      </c>
-      <c r="B123">
-        <f t="shared" ref="B123" si="115">B122</f>
-        <v>60</v>
-      </c>
-      <c r="C123" t="s">
-        <v>227</v>
-      </c>
-      <c r="D123" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124">
-        <f t="shared" si="61"/>
-        <v>122</v>
-      </c>
-      <c r="B124">
-        <f t="shared" ref="B124" si="116">B122+1</f>
-        <v>61</v>
-      </c>
-      <c r="C124" t="s">
-        <v>223</v>
-      </c>
-      <c r="D124" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <f t="shared" si="61"/>
-        <v>123</v>
-      </c>
-      <c r="B125">
-        <f t="shared" ref="B125" si="117">B124</f>
-        <v>61</v>
-      </c>
-      <c r="C125" t="s">
-        <v>224</v>
-      </c>
-      <c r="D125" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126">
-        <f t="shared" si="61"/>
-        <v>124</v>
-      </c>
-      <c r="B126">
-        <f t="shared" ref="B126" si="118">B124+1</f>
-        <v>62</v>
-      </c>
-      <c r="C126" t="s">
-        <v>225</v>
-      </c>
-      <c r="D126" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127">
-        <f t="shared" si="61"/>
-        <v>125</v>
-      </c>
-      <c r="B127">
-        <f t="shared" ref="B127" si="119">B126</f>
-        <v>62</v>
-      </c>
-      <c r="C127" t="s">
-        <v>226</v>
-      </c>
-      <c r="D127" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128">
-        <f t="shared" si="61"/>
-        <v>126</v>
-      </c>
-      <c r="B128">
-        <f t="shared" ref="B128" si="120">B126+1</f>
-        <v>63</v>
-      </c>
-      <c r="C128" t="s">
-        <v>239</v>
-      </c>
-      <c r="D128" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129">
-        <f t="shared" si="61"/>
-        <v>127</v>
-      </c>
-      <c r="B129">
-        <f t="shared" ref="B129" si="121">B128</f>
-        <v>63</v>
-      </c>
-      <c r="C129" t="s">
-        <v>238</v>
-      </c>
-      <c r="D129" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <f t="shared" si="61"/>
-        <v>128</v>
-      </c>
-      <c r="B130">
-        <f t="shared" ref="B130" si="122">B128+1</f>
-        <v>64</v>
-      </c>
-      <c r="C130" t="s">
-        <v>237</v>
-      </c>
-      <c r="D130" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <f t="shared" si="61"/>
-        <v>129</v>
-      </c>
-      <c r="B131">
-        <f t="shared" ref="B131" si="123">B130</f>
-        <v>64</v>
-      </c>
-      <c r="C131" t="s">
-        <v>236</v>
-      </c>
-      <c r="D131" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <f t="shared" si="61"/>
-        <v>130</v>
-      </c>
-      <c r="B132">
-        <f t="shared" ref="B132" si="124">B130+1</f>
-        <v>65</v>
-      </c>
-      <c r="C132" t="s">
-        <v>235</v>
-      </c>
-      <c r="D132" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133">
-        <f t="shared" si="61"/>
-        <v>131</v>
-      </c>
-      <c r="B133">
-        <f t="shared" ref="B133" si="125">B132</f>
-        <v>65</v>
-      </c>
-      <c r="C133" t="s">
-        <v>234</v>
-      </c>
-      <c r="D133" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134">
-        <f t="shared" ref="A134:A139" si="126">A133+1</f>
-        <v>132</v>
-      </c>
-      <c r="B134">
-        <f t="shared" ref="B134" si="127">B132+1</f>
-        <v>66</v>
-      </c>
-      <c r="C134" t="s">
-        <v>233</v>
-      </c>
-      <c r="D134" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135">
-        <f t="shared" si="126"/>
-        <v>133</v>
-      </c>
-      <c r="B135">
-        <f t="shared" ref="B135" si="128">B134</f>
-        <v>66</v>
-      </c>
-      <c r="C135" t="s">
-        <v>232</v>
-      </c>
-      <c r="D135" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136">
-        <f t="shared" si="126"/>
-        <v>134</v>
-      </c>
-      <c r="B136">
-        <f>B134+1</f>
-        <v>67</v>
-      </c>
-      <c r="C136" t="s">
-        <v>231</v>
-      </c>
-      <c r="D136" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137">
-        <f t="shared" si="126"/>
-        <v>135</v>
-      </c>
-      <c r="B137">
-        <f t="shared" ref="B137:B139" si="129">B136</f>
-        <v>67</v>
-      </c>
-      <c r="C137" t="s">
-        <v>230</v>
-      </c>
-      <c r="D137" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138">
-        <f t="shared" si="126"/>
-        <v>136</v>
-      </c>
-      <c r="B138">
-        <f>B137+1</f>
-        <v>68</v>
-      </c>
-      <c r="C138" t="s">
-        <v>229</v>
-      </c>
-      <c r="D138" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139">
-        <f t="shared" si="126"/>
-        <v>137</v>
-      </c>
-      <c r="B139">
-        <f t="shared" si="129"/>
-        <v>68</v>
-      </c>
-      <c r="C139" t="s">
-        <v>228</v>
-      </c>
-      <c r="D139" t="s">
         <v>204</v>
       </c>
     </row>

--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\dev\FLOWER-board-firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69701C28-00A0-4286-996E-2D1F345790AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642C969E-A069-487E-936E-D89E77AE0FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registers" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="255">
   <si>
     <t>Register Map</t>
   </si>
@@ -778,6 +778,30 @@
   </si>
   <si>
     <t>lower 12 bits are threshold offset (ie. Bumps all SBC thresholds up by x amount)</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 1 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 2 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 3 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 4 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 5 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 6 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 7 thresholds</t>
+  </si>
+  <si>
+    <t>phased trigger-&gt; beam 8 thresholds</t>
   </si>
 </sst>
 </file>
@@ -979,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1076,6 +1100,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3587,7 +3612,7 @@
         <v>x81</v>
       </c>
       <c r="C136" s="40" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="D136" s="40" t="s">
         <v>228</v>
@@ -3606,7 +3631,7 @@
         <v>x82</v>
       </c>
       <c r="C137" s="40" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="D137" s="40" t="s">
         <v>228</v>
@@ -3625,7 +3650,7 @@
         <v>x83</v>
       </c>
       <c r="C138" s="40" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="D138" s="40" t="s">
         <v>228</v>
@@ -3644,7 +3669,7 @@
         <v>x84</v>
       </c>
       <c r="C139" s="40" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="D139" s="40" t="s">
         <v>228</v>
@@ -3663,7 +3688,7 @@
         <v>x85</v>
       </c>
       <c r="C140" s="40" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="D140" s="40" t="s">
         <v>228</v>
@@ -3682,7 +3707,7 @@
         <v>x86</v>
       </c>
       <c r="C141" s="40" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="D141" s="40" t="s">
         <v>228</v>
@@ -3701,7 +3726,7 @@
         <v>x87</v>
       </c>
       <c r="C142" s="40" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="D142" s="40" t="s">
         <v>228</v>
@@ -3720,7 +3745,7 @@
         <v>x88</v>
       </c>
       <c r="C143" s="40" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="D143" s="40" t="s">
         <v>228</v>
@@ -3738,15 +3763,9 @@
         <f t="shared" si="5"/>
         <v>x89</v>
       </c>
-      <c r="C144" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D144" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E144" s="40" t="s">
-        <v>229</v>
-      </c>
+      <c r="C144" s="46"/>
+      <c r="D144" s="46"/>
+      <c r="E144" s="46"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
@@ -3757,15 +3776,9 @@
         <f t="shared" si="5"/>
         <v>x8A</v>
       </c>
-      <c r="C145" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D145" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E145" s="40" t="s">
-        <v>229</v>
-      </c>
+      <c r="C145" s="46"/>
+      <c r="D145" s="46"/>
+      <c r="E145" s="46"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
@@ -3776,15 +3789,9 @@
         <f t="shared" si="5"/>
         <v>x8B</v>
       </c>
-      <c r="C146" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D146" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E146" s="40" t="s">
-        <v>229</v>
-      </c>
+      <c r="C146" s="46"/>
+      <c r="D146" s="46"/>
+      <c r="E146" s="46"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
@@ -3795,15 +3802,6 @@
         <f t="shared" si="5"/>
         <v>x8C</v>
       </c>
-      <c r="C147" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D147" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E147" s="40" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
@@ -3814,15 +3812,6 @@
         <f t="shared" si="5"/>
         <v>x8D</v>
       </c>
-      <c r="C148" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D148" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E148" s="40" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
@@ -3833,15 +3822,6 @@
         <f t="shared" si="5"/>
         <v>x8E</v>
       </c>
-      <c r="C149" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D149" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E149" s="40" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
@@ -3851,15 +3831,6 @@
       <c r="B150" s="16" t="str">
         <f t="shared" si="5"/>
         <v>x8F</v>
-      </c>
-      <c r="C150" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="D150" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E150" s="40" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -6092,7 +6063,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
-        <f t="shared" ref="A70:A133" si="61">A69+1</f>
+        <f t="shared" ref="A70:A97" si="61">A69+1</f>
         <v>68</v>
       </c>
       <c r="B70">

--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\dev\FLOWER-board-firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015CDA2A-6F70-4FDF-9EEE-55169E325FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504BD9E-65F3-49C9-BE3B-D66890D3703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="261">
   <si>
     <t>Register Map</t>
   </si>
@@ -814,6 +814,12 @@
   </si>
   <si>
     <t>high byte contains station that the firmware was compile for</t>
+  </si>
+  <si>
+    <t>READ ONLY</t>
+  </si>
+  <si>
+    <t>test burst read</t>
   </si>
 </sst>
 </file>
@@ -929,7 +935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1017,11 +1023,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1118,7 +1133,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1492,8 +1515,11 @@
         <v>66</v>
       </c>
       <c r="F7"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="46" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1507,6 +1533,7 @@
       <c r="D8" t="s">
         <v>16</v>
       </c>
+      <c r="G8" s="47"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -1526,6 +1553,7 @@
       <c r="F9" s="3" t="s">
         <v>258</v>
       </c>
+      <c r="G9" s="47"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -1545,6 +1573,7 @@
       <c r="F10" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="G10" s="47"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -1564,6 +1593,7 @@
       <c r="F11" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="G11" s="47"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -1583,6 +1613,7 @@
       <c r="F12" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="G12" s="47"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -1602,6 +1633,7 @@
       <c r="F13" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="G13" s="47"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -1618,6 +1650,7 @@
       <c r="D14" t="s">
         <v>159</v>
       </c>
+      <c r="G14" s="47"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -1634,6 +1667,7 @@
       <c r="D15" s="34" t="s">
         <v>16</v>
       </c>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -1650,8 +1684,9 @@
       <c r="D16" s="34" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="47"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -1672,8 +1707,9 @@
       <c r="F17" s="11" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="47"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -1692,8 +1728,9 @@
         <v>6</v>
       </c>
       <c r="F18" s="13"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="47"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -1712,8 +1749,9 @@
         <v>6</v>
       </c>
       <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="47"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -1732,8 +1770,9 @@
         <v>6</v>
       </c>
       <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="47"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -1752,8 +1791,9 @@
         <v>6</v>
       </c>
       <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="47"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -1769,8 +1809,9 @@
         <v>168</v>
       </c>
       <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="47"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -1789,8 +1830,9 @@
         <v>6</v>
       </c>
       <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="47"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -1809,8 +1851,9 @@
         <v>6</v>
       </c>
       <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="47"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="12">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -1829,8 +1872,9 @@
         <v>6</v>
       </c>
       <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="47"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="12">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -1840,8 +1884,9 @@
         <v>x13</v>
       </c>
       <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="47"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="12">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -1851,8 +1896,9 @@
         <v>x14</v>
       </c>
       <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="47"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -1862,8 +1908,9 @@
         <v>x15</v>
       </c>
       <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="47"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="12">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -1873,8 +1920,9 @@
         <v>x16</v>
       </c>
       <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="47"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -1884,8 +1932,9 @@
         <v>x17</v>
       </c>
       <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="47"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="12">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -1895,8 +1944,9 @@
         <v>x18</v>
       </c>
       <c r="F31" s="13"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="47"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -1906,8 +1956,9 @@
         <v>x19</v>
       </c>
       <c r="F32" s="13"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="47"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="12">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -1917,8 +1968,9 @@
         <v>x1A</v>
       </c>
       <c r="F33" s="13"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="47"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -1928,8 +1980,9 @@
         <v>x1B</v>
       </c>
       <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="47"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -1939,8 +1992,9 @@
         <v>x1C</v>
       </c>
       <c r="F35" s="13"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="47"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -1950,8 +2004,9 @@
         <v>x1D</v>
       </c>
       <c r="F36" s="13"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="47"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="12">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -1961,8 +2016,9 @@
         <v>x1E</v>
       </c>
       <c r="F37" s="13"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="47"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -1972,8 +2028,9 @@
         <v>x1F</v>
       </c>
       <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="47"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="12">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -1983,8 +2040,9 @@
         <v>x20</v>
       </c>
       <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="47"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -1994,8 +2052,9 @@
         <v>x21</v>
       </c>
       <c r="F40" s="13"/>
-    </row>
-    <row r="41" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G40" s="47"/>
+    </row>
+    <row r="41" spans="1:7" s="25" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="28">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -2010,8 +2069,9 @@
       <c r="D41" s="30"/>
       <c r="E41" s="30"/>
       <c r="F41" s="31"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="48"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -2030,7 +2090,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -2049,7 +2109,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -2068,7 +2128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -2087,7 +2147,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -2109,7 +2169,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -2128,7 +2188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -2239,6 +2299,9 @@
         <f t="shared" si="0"/>
         <v>x2F</v>
       </c>
+      <c r="C54" t="s">
+        <v>260</v>
+      </c>
       <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -3841,8 +3904,6 @@
         <f t="shared" si="5"/>
         <v>x8C</v>
       </c>
-      <c r="C147" s="46"/>
-      <c r="D147" s="46"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
@@ -3853,8 +3914,6 @@
         <f t="shared" si="5"/>
         <v>x8D</v>
       </c>
-      <c r="C148" s="46"/>
-      <c r="D148" s="46"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
@@ -3865,8 +3924,6 @@
         <f t="shared" si="5"/>
         <v>x8E</v>
       </c>
-      <c r="C149" s="46"/>
-      <c r="D149" s="46"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
@@ -3877,8 +3934,6 @@
         <f t="shared" si="5"/>
         <v>x8F</v>
       </c>
-      <c r="C150" s="46"/>
-      <c r="D150" s="46"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
@@ -5001,11 +5056,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G7:G41"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\dev\FLOWER-board-firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504BD9E-65F3-49C9-BE3B-D66890D3703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FEC9C1-0186-4825-89E4-A8335B3258A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registers" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="265">
   <si>
     <t>Register Map</t>
   </si>
@@ -820,6 +820,18 @@
   </si>
   <si>
     <t>test burst read</t>
+  </si>
+  <si>
+    <t>phased trigger -&gt; ch0 and ch1 fine gain equalization</t>
+  </si>
+  <si>
+    <t>phased trigger -&gt; ch2 and ch3 fine gain equalization</t>
+  </si>
+  <si>
+    <t>First byte, lower 5 bits for ch 0. Second byte, lower 5 bits for ch 1. (64-number)*samples/64</t>
+  </si>
+  <si>
+    <t>First byte, lower 5 bits for ch 2. Second byte, lower 5 bits for ch 3. (64-number)*samples/64</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3904,6 +3916,15 @@
         <f t="shared" si="5"/>
         <v>x8C</v>
       </c>
+      <c r="C147" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="D147" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="E147" s="40" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
@@ -3913,6 +3934,15 @@
       <c r="B148" s="16" t="str">
         <f t="shared" si="5"/>
         <v>x8D</v>
+      </c>
+      <c r="C148" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="D148" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="E148" s="40" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">

--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\dev\FLOWER-board-firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FEC9C1-0186-4825-89E4-A8335B3258A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504BD9E-65F3-49C9-BE3B-D66890D3703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registers" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="261">
   <si>
     <t>Register Map</t>
   </si>
@@ -820,18 +820,6 @@
   </si>
   <si>
     <t>test burst read</t>
-  </si>
-  <si>
-    <t>phased trigger -&gt; ch0 and ch1 fine gain equalization</t>
-  </si>
-  <si>
-    <t>phased trigger -&gt; ch2 and ch3 fine gain equalization</t>
-  </si>
-  <si>
-    <t>First byte, lower 5 bits for ch 0. Second byte, lower 5 bits for ch 1. (64-number)*samples/64</t>
-  </si>
-  <si>
-    <t>First byte, lower 5 bits for ch 2. Second byte, lower 5 bits for ch 3. (64-number)*samples/64</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3916,15 +3904,6 @@
         <f t="shared" si="5"/>
         <v>x8C</v>
       </c>
-      <c r="C147" s="40" t="s">
-        <v>261</v>
-      </c>
-      <c r="D147" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="E147" s="40" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
@@ -3934,15 +3913,6 @@
       <c r="B148" s="16" t="str">
         <f t="shared" si="5"/>
         <v>x8D</v>
-      </c>
-      <c r="C148" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="D148" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="E148" s="40" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">

--- a/doc/flower-register-map.xlsx
+++ b/doc/flower-register-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryank\Documents\firmware\rnog\dev\FLOWER-board-firmware\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504BD9E-65F3-49C9-BE3B-D66890D3703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85451262-C064-4DD7-9442-C5949AFC11AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="228" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registers" sheetId="1" r:id="rId1"/>
@@ -1136,7 +1136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
